--- a/data/analysis_gemini_3_6_flash_qwen2_audio/multimodal_event_eval_gemini_3_6_flash_qwen2_audio_w1_0s_h1_0s.xlsx
+++ b/data/analysis_gemini_3_6_flash_qwen2_audio/multimodal_event_eval_gemini_3_6_flash_qwen2_audio_w1_0s_h1_0s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="52">
   <si>
     <t>event</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>sound: impact(0-144), sound: impact(192-216), sound: shout(24-48), sound: shout(144-240), visual: enter_or_exit_vehicle(48-168), visual: running(0-48), visual: suspicious_near_vehicle(48-168)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(48-168), visual: running(0-48), visual: suspicious_near_vehicle(48-168)</t>
   </si>
   <si>
     <t>sound: impact(0-24), sound: impact(72-144), sound: impact(192-240), sound: shout(24-192), visual: enter_or_exit_vehicle(48-168), visual: running(0-24), visual: suspicious_near_vehicle(48-144)</t>
@@ -666,22 +669,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -1542,6 +1545,67 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -1564,63 +1628,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>32</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1664,7 +1684,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1681,7 +1701,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1725,7 +1745,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1769,7 +1789,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1807,13 +1827,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>48</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1901,7 +1921,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1945,7 +1965,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
